--- a/enhancements/test-files/13_MoneyDates_pc0909_2026.xlsx
+++ b/enhancements/test-files/13_MoneyDates_pc0909_2026.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,10 +558,35 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45816</v>
+        <v>45882</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46082</v>
+        <v>46081</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1176.38</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>799.9400000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>376.44</v>
       </c>
     </row>
     <row r="3">
@@ -533,12 +600,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -557,10 +624,35 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46040</v>
+        <v>45957</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46080</v>
+        <v>46084</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>252.86</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="P3" t="n">
+        <v>146.66</v>
       </c>
     </row>
     <row r="4">
@@ -579,7 +671,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -598,10 +690,35 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45938</v>
+        <v>45983</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46087</v>
+        <v>46088</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2928.71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1669.36</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1259.35</v>
       </c>
     </row>
     <row r="5">
@@ -615,12 +732,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -639,10 +756,35 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45803</v>
+        <v>46027</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46086</v>
+        <v>46090</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>624.54</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="P5" t="n">
+        <v>262.31</v>
       </c>
     </row>
     <row r="6">
@@ -656,12 +798,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -680,10 +822,35 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45980</v>
+        <v>45849</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46092</v>
+        <v>46089</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1408.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>647.86</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P6" t="n">
+        <v>760.53</v>
       </c>
     </row>
     <row r="7">
@@ -697,12 +864,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -721,10 +888,35 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45864</v>
+        <v>45838</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46094</v>
+        <v>46096</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1129.28</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>688.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P7" t="n">
+        <v>440.42</v>
       </c>
     </row>
   </sheetData>
